--- a/dados/perfis/tecnologo_automacao_2027_1/matriz_curricular.xlsx
+++ b/dados/perfis/tecnologo_automacao_2027_1/matriz_curricular.xlsx
@@ -6964,7 +6964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V160"/>
+  <dimension ref="A1:T160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.140625" customWidth="1" style="84" min="1" max="1"/>
@@ -7054,50 +7054,40 @@
       </c>
       <c r="M1" s="85" t="inlineStr">
         <is>
-          <t>unidade_oferta</t>
+          <t>pre_requisitos</t>
         </is>
       </c>
       <c r="N1" s="85" t="inlineStr">
         <is>
-          <t>pre_requisitos</t>
+          <t>correquisitos</t>
         </is>
       </c>
       <c r="O1" s="85" t="inlineStr">
         <is>
-          <t>correquisitos</t>
+          <t>areas</t>
         </is>
       </c>
       <c r="P1" s="85" t="inlineStr">
         <is>
-          <t>areas</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="Q1" s="85" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>conteudos</t>
         </is>
       </c>
       <c r="R1" s="85" t="inlineStr">
         <is>
-          <t>conteudos</t>
+          <t>competencias</t>
         </is>
       </c>
       <c r="S1" s="85" t="inlineStr">
         <is>
-          <t>competencias</t>
+          <t>ativo</t>
         </is>
       </c>
       <c r="T1" s="85" t="inlineStr">
-        <is>
-          <t>ativo</t>
-        </is>
-      </c>
-      <c r="U1" s="85" t="inlineStr">
-        <is>
-          <t>codigo_provisorio</t>
-        </is>
-      </c>
-      <c r="V1" s="85" t="inlineStr">
         <is>
           <t>observacoes</t>
         </is>
@@ -7140,10 +7130,7 @@
       <c r="L2" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T2" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" s="84" t="b">
+      <c r="S2" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7192,26 +7179,23 @@
       <c r="L3" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N3" s="84" t="inlineStr">
+      <c r="M3" s="84" t="inlineStr">
         <is>
           <t>FAMAT31021</t>
         </is>
       </c>
-      <c r="P3" s="84" t="inlineStr">
+      <c r="O3" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R3" s="84" t="inlineStr">
+      <c r="Q3" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_21, DCN_BASE_22</t>
         </is>
       </c>
-      <c r="T3" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="84" t="b">
-        <v>0</v>
+      <c r="S3" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -7251,10 +7235,7 @@
       <c r="L4" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T4" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="84" t="b">
+      <c r="S4" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7295,10 +7276,7 @@
       <c r="L5" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T5" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" s="84" t="b">
+      <c r="S5" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7347,25 +7325,22 @@
       <c r="L6" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N6" s="84" t="inlineStr">
+      <c r="M6" s="84" t="inlineStr">
         <is>
           <t>FEELT!ED</t>
         </is>
       </c>
-      <c r="P6" s="84" t="inlineStr">
+      <c r="O6" s="84" t="inlineStr">
         <is>
           <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
       </c>
-      <c r="R6" s="84" t="inlineStr">
+      <c r="Q6" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_29, DCN_BASE_31, DCN_BASE_23</t>
         </is>
       </c>
-      <c r="T6" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="84" t="b">
+      <c r="S6" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7414,25 +7389,22 @@
       <c r="L7" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N7" s="84" t="inlineStr">
+      <c r="M7" s="84" t="inlineStr">
         <is>
           <t>FEELT!AMAQ</t>
         </is>
       </c>
-      <c r="P7" s="84" t="inlineStr">
+      <c r="O7" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R7" s="84" t="inlineStr">
+      <c r="Q7" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_06, DCN_BASE_34, DCN_BASE_07</t>
         </is>
       </c>
-      <c r="T7" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="84" t="b">
+      <c r="S7" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7481,25 +7453,22 @@
       <c r="L8" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="84" t="inlineStr">
+      <c r="M8" s="84" t="inlineStr">
         <is>
           <t>FAMAT31032, FEELT!FIA</t>
         </is>
       </c>
-      <c r="P8" s="84" t="inlineStr">
+      <c r="O8" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R8" s="84" t="inlineStr">
+      <c r="Q8" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_06, DCN_BASE_25, DCN_BASE_34</t>
         </is>
       </c>
-      <c r="T8" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="84" t="b">
+      <c r="S8" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7540,10 +7509,7 @@
       <c r="L9" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T9" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" s="84" t="b">
+      <c r="S9" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7584,10 +7550,7 @@
       <c r="L10" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T10" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" s="84" t="b">
+      <c r="S10" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7636,25 +7599,22 @@
       <c r="L11" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N11" s="84" t="inlineStr">
+      <c r="M11" s="84" t="inlineStr">
         <is>
           <t>FEELT!ESOF, FEELT31724</t>
         </is>
       </c>
-      <c r="P11" s="84" t="inlineStr">
+      <c r="O11" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R11" s="84" t="inlineStr">
+      <c r="Q11" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_02, DCN_BASE_15, DCN_BASE_14</t>
         </is>
       </c>
-      <c r="T11" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U11" s="84" t="b">
+      <c r="S11" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7703,25 +7663,22 @@
       <c r="L12" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N12" s="84" t="inlineStr">
+      <c r="M12" s="84" t="inlineStr">
         <is>
           <t>FEELT!ESC</t>
         </is>
       </c>
-      <c r="P12" s="84" t="inlineStr">
+      <c r="O12" s="84" t="inlineStr">
         <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R12" s="84" t="inlineStr">
+      <c r="Q12" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_38</t>
         </is>
       </c>
-      <c r="T12" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U12" s="84" t="b">
+      <c r="S12" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7770,16 +7727,13 @@
       <c r="L13" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N13" s="84" t="inlineStr">
+      <c r="M13" s="84" t="inlineStr">
         <is>
           <t>FEELT!PP</t>
         </is>
       </c>
-      <c r="T13" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13" s="84" t="b">
-        <v>1</v>
+      <c r="S13" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7812,16 +7766,13 @@
       <c r="L14" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P14" s="84" t="inlineStr">
+      <c r="O14" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_COMPLEMENTAR_GERAL</t>
         </is>
       </c>
-      <c r="T14" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U14" s="84" t="b">
-        <v>0</v>
+      <c r="S14" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -7854,21 +7805,18 @@
       <c r="L15" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N15" s="84" t="inlineStr">
+      <c r="M15" s="84" t="inlineStr">
         <is>
           <t>&gt;=1875h</t>
         </is>
       </c>
-      <c r="P15" s="84" t="inlineStr">
+      <c r="O15" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_TECNOLOGICA_GERAL</t>
         </is>
       </c>
-      <c r="T15" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U15" s="84" t="b">
-        <v>0</v>
+      <c r="S15" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -7916,21 +7864,18 @@
       <c r="L16" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="P16" s="84" t="inlineStr">
+      <c r="O16" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_HUMANISTICA_GERAL</t>
         </is>
       </c>
-      <c r="R16" s="84" t="inlineStr">
+      <c r="Q16" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_42</t>
         </is>
       </c>
-      <c r="T16" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U16" s="84" t="b">
-        <v>0</v>
+      <c r="S16" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -7978,26 +7923,23 @@
       <c r="L17" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N17" s="84" t="inlineStr">
+      <c r="M17" s="84" t="inlineStr">
         <is>
           <t>ACE1</t>
         </is>
       </c>
-      <c r="P17" s="84" t="inlineStr">
+      <c r="O17" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_HUMANISTICA_GERAL</t>
         </is>
       </c>
-      <c r="R17" s="84" t="inlineStr">
+      <c r="Q17" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_42</t>
         </is>
       </c>
-      <c r="T17" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U17" s="84" t="b">
-        <v>0</v>
+      <c r="S17" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -8045,26 +7987,23 @@
       <c r="L18" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N18" s="84" t="inlineStr">
+      <c r="M18" s="84" t="inlineStr">
         <is>
           <t>ACE2</t>
         </is>
       </c>
-      <c r="P18" s="84" t="inlineStr">
+      <c r="O18" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_HUMANISTICA_GERAL</t>
         </is>
       </c>
-      <c r="R18" s="84" t="inlineStr">
+      <c r="Q18" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_42</t>
         </is>
       </c>
-      <c r="T18" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U18" s="84" t="b">
-        <v>0</v>
+      <c r="S18" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -8112,26 +8051,23 @@
       <c r="L19" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N19" s="84" t="inlineStr">
+      <c r="M19" s="84" t="inlineStr">
         <is>
           <t>ACE3</t>
         </is>
       </c>
-      <c r="P19" s="84" t="inlineStr">
+      <c r="O19" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_HUMANISTICA_GERAL</t>
         </is>
       </c>
-      <c r="R19" s="84" t="inlineStr">
+      <c r="Q19" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_42</t>
         </is>
       </c>
-      <c r="T19" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U19" s="84" t="b">
-        <v>0</v>
+      <c r="S19" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -8179,25 +8115,22 @@
       <c r="L20" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N20" s="84" t="inlineStr">
+      <c r="M20" s="84" t="inlineStr">
         <is>
           <t>FEELT!ED</t>
         </is>
       </c>
-      <c r="P20" s="84" t="inlineStr">
+      <c r="O20" s="84" t="inlineStr">
         <is>
           <t>CC2020_MODELAGEM_SISTEMAS</t>
         </is>
       </c>
-      <c r="R20" s="84" t="inlineStr">
+      <c r="Q20" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_09, DCN_BASE_33</t>
         </is>
       </c>
-      <c r="T20" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U20" s="84" t="b">
+      <c r="S20" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8238,10 +8171,7 @@
       <c r="L21" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T21" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21" s="84" t="b">
+      <c r="S21" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8290,21 +8220,18 @@
       <c r="L22" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P22" s="84" t="inlineStr">
+      <c r="O22" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R22" s="84" t="inlineStr">
+      <c r="Q22" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22</t>
         </is>
       </c>
-      <c r="T22" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U22" s="84" t="b">
-        <v>0</v>
+      <c r="S22" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -8352,26 +8279,23 @@
       <c r="L23" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N23" s="84" t="inlineStr">
+      <c r="M23" s="84" t="inlineStr">
         <is>
           <t>FAMAT31011</t>
         </is>
       </c>
-      <c r="P23" s="84" t="inlineStr">
+      <c r="O23" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R23" s="84" t="inlineStr">
+      <c r="Q23" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22</t>
         </is>
       </c>
-      <c r="T23" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U23" s="84" t="b">
-        <v>0</v>
+      <c r="S23" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -8419,26 +8343,23 @@
       <c r="L24" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N24" s="84" t="inlineStr">
+      <c r="M24" s="84" t="inlineStr">
         <is>
           <t>FAMAT31012</t>
         </is>
       </c>
-      <c r="P24" s="84" t="inlineStr">
+      <c r="O24" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R24" s="84" t="inlineStr">
+      <c r="Q24" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22</t>
         </is>
       </c>
-      <c r="T24" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U24" s="84" t="b">
-        <v>0</v>
+      <c r="S24" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -8486,26 +8407,23 @@
       <c r="L25" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N25" s="84" t="inlineStr">
+      <c r="M25" s="84" t="inlineStr">
         <is>
           <t>FAMAT31013, FAMAT31022</t>
         </is>
       </c>
-      <c r="P25" s="84" t="inlineStr">
+      <c r="O25" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R25" s="84" t="inlineStr">
+      <c r="Q25" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22, DCN_BASE_34</t>
         </is>
       </c>
-      <c r="T25" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U25" s="84" t="b">
-        <v>0</v>
+      <c r="S25" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -8545,10 +8463,7 @@
       <c r="L26" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U26" s="84" t="b">
+      <c r="S26" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8589,10 +8504,7 @@
       <c r="L27" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T27" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U27" s="84" t="b">
+      <c r="S27" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8633,10 +8545,7 @@
       <c r="L28" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T28" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U28" s="84" t="b">
+      <c r="S28" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8677,10 +8586,7 @@
       <c r="L29" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T29" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U29" s="84" t="b">
+      <c r="S29" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8721,10 +8627,7 @@
       <c r="L30" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T30" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U30" s="84" t="b">
+      <c r="S30" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8765,10 +8668,7 @@
       <c r="L31" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T31" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U31" s="84" t="b">
+      <c r="S31" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8809,10 +8709,7 @@
       <c r="L32" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T32" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U32" s="84" t="b">
+      <c r="S32" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8861,26 +8758,23 @@
       <c r="L33" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N33" s="84" t="inlineStr">
+      <c r="M33" s="84" t="inlineStr">
         <is>
           <t>INFIS39033</t>
         </is>
       </c>
-      <c r="P33" s="84" t="inlineStr">
+      <c r="O33" s="84" t="inlineStr">
         <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R33" s="84" t="inlineStr">
+      <c r="Q33" s="84" t="inlineStr">
         <is>
           <t>DCN_TEC_12, DCN_TEC_13</t>
         </is>
       </c>
-      <c r="T33" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U33" s="84" t="b">
-        <v>0</v>
+      <c r="S33" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -8928,36 +8822,33 @@
       <c r="L34" s="84" t="b">
         <v>1</v>
       </c>
+      <c r="M34" s="84" t="inlineStr">
+        <is>
+          <t>FEELT31204</t>
+        </is>
+      </c>
       <c r="N34" s="84" t="inlineStr">
         <is>
-          <t>FEELT31204</t>
+          <t>FEELT31301</t>
         </is>
       </c>
       <c r="O34" s="84" t="inlineStr">
         <is>
-          <t>FEELT31301</t>
+          <t>CC2020_HARDWARE</t>
         </is>
       </c>
       <c r="P34" s="84" t="inlineStr">
         <is>
-          <t>CC2020_HARDWARE</t>
+          <t>EDUCACAO_AMBIENTAL, PREVENCAO_DESASTRES</t>
         </is>
       </c>
       <c r="Q34" s="84" t="inlineStr">
         <is>
-          <t>EDUCACAO_AMBIENTAL, PREVENCAO_DESASTRES</t>
-        </is>
-      </c>
-      <c r="R34" s="84" t="inlineStr">
-        <is>
           <t>DCN_TEC_12, DCN_TEC_13</t>
         </is>
       </c>
-      <c r="T34" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U34" s="84" t="b">
-        <v>0</v>
+      <c r="S34" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -8997,11 +8888,8 @@
       <c r="L35" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T35" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U35" s="84" t="b">
-        <v>1</v>
+      <c r="S35" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -9041,15 +8929,12 @@
       <c r="L36" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="R36" s="84" t="inlineStr">
+      <c r="Q36" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_01</t>
         </is>
       </c>
-      <c r="T36" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U36" s="84" t="b">
+      <c r="S36" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9098,16 +8983,13 @@
       <c r="L37" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="P37" s="84" t="inlineStr">
+      <c r="O37" s="84" t="inlineStr">
         <is>
           <t>CC2020_USUARIOS_ORGANIZACOES</t>
         </is>
       </c>
-      <c r="T37" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U37" s="84" t="b">
-        <v>1</v>
+      <c r="S37" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -9147,16 +9029,13 @@
       <c r="L38" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N38" s="84" t="inlineStr">
+      <c r="M38" s="84" t="inlineStr">
         <is>
           <t>FEELT!FIA</t>
         </is>
       </c>
-      <c r="T38" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U38" s="84" t="b">
-        <v>1</v>
+      <c r="S38" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -9196,10 +9075,7 @@
       <c r="L39" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T39" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U39" s="84" t="b">
+      <c r="S39" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9240,10 +9116,7 @@
       <c r="L40" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T40" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U40" s="84" t="b">
+      <c r="S40" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9284,20 +9157,17 @@
       <c r="L41" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N41" s="84" t="inlineStr">
+      <c r="M41" s="84" t="inlineStr">
         <is>
           <t>FAMAT31022</t>
         </is>
       </c>
-      <c r="R41" s="84" t="inlineStr">
+      <c r="Q41" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_08, DCN_BASE_17</t>
         </is>
       </c>
-      <c r="T41" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U41" s="84" t="b">
+      <c r="S41" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9338,11 +9208,8 @@
       <c r="L42" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T42" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U42" s="84" t="b">
-        <v>1</v>
+      <c r="S42" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -9382,10 +9249,7 @@
       <c r="L43" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T43" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U43" s="84" t="b">
+      <c r="S43" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9426,10 +9290,7 @@
       <c r="L44" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T44" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U44" s="84" t="b">
+      <c r="S44" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9470,10 +9331,7 @@
       <c r="L45" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T45" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U45" s="84" t="b">
+      <c r="S45" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9514,10 +9372,7 @@
       <c r="L46" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T46" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U46" s="84" t="b">
+      <c r="S46" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9558,10 +9413,7 @@
       <c r="L47" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T47" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U47" s="84" t="b">
+      <c r="S47" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9602,10 +9454,7 @@
       <c r="L48" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T48" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U48" s="84" t="b">
+      <c r="S48" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9646,15 +9495,12 @@
       <c r="L49" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="Q49" s="84" t="inlineStr">
+      <c r="P49" s="84" t="inlineStr">
         <is>
           <t>RELACOES_ETNICO_RACIAIS, DIREITOS_HUMANOS, EDUCACAO_AMBIENTAL</t>
         </is>
       </c>
-      <c r="T49" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U49" s="84" t="b">
+      <c r="S49" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9688,16 +9534,13 @@
       <c r="L50" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="P50" s="84" t="inlineStr">
+      <c r="O50" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_COMPLEMENTAR_GERAL</t>
         </is>
       </c>
-      <c r="T50" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U50" s="84" t="b">
-        <v>0</v>
+      <c r="S50" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -9745,25 +9588,22 @@
       <c r="L51" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N51" s="84" t="inlineStr">
+      <c r="M51" s="84" t="inlineStr">
         <is>
           <t>FEELT31409</t>
         </is>
       </c>
-      <c r="P51" s="84" t="inlineStr">
+      <c r="O51" s="84" t="inlineStr">
         <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R51" s="84" t="inlineStr">
+      <c r="Q51" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_38, DCN_BASE_37, DCN_BASE_01, DCN_TEC_10, DCN_TEC_00, DCN_TEC_02, DCN_TEC_01</t>
         </is>
       </c>
-      <c r="T51" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U51" s="84" t="b">
+      <c r="S51" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9812,26 +9652,23 @@
       <c r="L52" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N52" s="84" t="inlineStr">
+      <c r="M52" s="84" t="inlineStr">
         <is>
           <t>FEELT31301</t>
         </is>
       </c>
-      <c r="P52" s="84" t="inlineStr">
+      <c r="O52" s="84" t="inlineStr">
         <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R52" s="84" t="inlineStr">
+      <c r="Q52" s="84" t="inlineStr">
         <is>
           <t>DCN_TEC_11, DCN_TEC_02, DCN_TEC_12, DCN_TEC_08</t>
         </is>
       </c>
-      <c r="T52" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U52" s="84" t="b">
-        <v>0</v>
+      <c r="S52" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -9879,26 +9716,23 @@
       <c r="L53" s="84" t="b">
         <v>1</v>
       </c>
+      <c r="N53" s="84" t="inlineStr">
+        <is>
+          <t>FEELT31401</t>
+        </is>
+      </c>
       <c r="O53" s="84" t="inlineStr">
         <is>
-          <t>FEELT31401</t>
-        </is>
-      </c>
-      <c r="P53" s="84" t="inlineStr">
-        <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R53" s="84" t="inlineStr">
+      <c r="Q53" s="84" t="inlineStr">
         <is>
           <t>DCN_TEC_11, DCN_TEC_02, DCN_TEC_12, DCN_TEC_08</t>
         </is>
       </c>
-      <c r="T53" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U53" s="84" t="b">
-        <v>0</v>
+      <c r="S53" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -9938,15 +9772,12 @@
       <c r="L54" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N54" s="84" t="inlineStr">
+      <c r="M54" s="84" t="inlineStr">
         <is>
           <t>FEELT31401</t>
         </is>
       </c>
-      <c r="T54" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U54" s="84" t="b">
+      <c r="S54" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9987,15 +9818,12 @@
       <c r="L55" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="O55" s="84" t="inlineStr">
+      <c r="N55" s="84" t="inlineStr">
         <is>
           <t>FEELT32502</t>
         </is>
       </c>
-      <c r="T55" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U55" s="84" t="b">
+      <c r="S55" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10044,21 +9872,18 @@
       <c r="L56" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P56" s="84" t="inlineStr">
+      <c r="O56" s="84" t="inlineStr">
         <is>
           <t>CC2020_USUARIOS_ORGANIZACOES</t>
         </is>
       </c>
-      <c r="R56" s="84" t="inlineStr">
+      <c r="Q56" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_41, DCN_BASE_46</t>
         </is>
       </c>
-      <c r="T56" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U56" s="84" t="b">
-        <v>0</v>
+      <c r="S56" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -10106,25 +9931,22 @@
       <c r="L57" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N57" s="84" t="inlineStr">
+      <c r="M57" s="84" t="inlineStr">
         <is>
           <t>FEELT!APMG</t>
         </is>
       </c>
-      <c r="P57" s="84" t="inlineStr">
+      <c r="O57" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R57" s="84" t="inlineStr">
+      <c r="Q57" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_06, DCN_BASE_42, DCN_BASE_40, DCN_BASE_03</t>
         </is>
       </c>
-      <c r="T57" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U57" s="84" t="b">
+      <c r="S57" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10173,25 +9995,22 @@
       <c r="L58" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N58" s="84" t="inlineStr">
+      <c r="M58" s="84" t="inlineStr">
         <is>
           <t>FEELT!BD, FEELT!POO</t>
         </is>
       </c>
-      <c r="P58" s="84" t="inlineStr">
+      <c r="O58" s="84" t="inlineStr">
         <is>
           <t>CC2020_DESENVOLVIMENTO_SOFTWARE</t>
         </is>
       </c>
-      <c r="R58" s="84" t="inlineStr">
+      <c r="Q58" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_36, DCN_BASE_02</t>
         </is>
       </c>
-      <c r="T58" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U58" s="84" t="b">
+      <c r="S58" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10240,21 +10059,18 @@
       <c r="L59" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P59" s="84" t="inlineStr">
+      <c r="O59" s="84" t="inlineStr">
         <is>
           <t>CC2020_USUARIOS_ORGANIZACOES</t>
         </is>
       </c>
-      <c r="R59" s="84" t="inlineStr">
+      <c r="Q59" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_47, DCN_BASE_46</t>
         </is>
       </c>
-      <c r="T59" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U59" s="84" t="b">
-        <v>0</v>
+      <c r="S59" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -10302,21 +10118,18 @@
       <c r="L60" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P60" s="84" t="inlineStr">
+      <c r="O60" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R60" s="84" t="inlineStr">
+      <c r="Q60" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_25</t>
         </is>
       </c>
-      <c r="T60" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U60" s="84" t="b">
-        <v>0</v>
+      <c r="S60" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -10364,25 +10177,22 @@
       <c r="L61" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N61" s="84" t="inlineStr">
+      <c r="M61" s="84" t="inlineStr">
         <is>
           <t>FEELT!PP</t>
         </is>
       </c>
-      <c r="P61" s="84" t="inlineStr">
+      <c r="O61" s="84" t="inlineStr">
         <is>
           <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
       </c>
-      <c r="R61" s="84" t="inlineStr">
+      <c r="Q61" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_31, DCN_BASE_33</t>
         </is>
       </c>
-      <c r="T61" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U61" s="84" t="b">
+      <c r="S61" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10423,11 +10233,8 @@
       <c r="L62" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T62" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U62" s="84" t="b">
-        <v>1</v>
+      <c r="S62" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -10467,11 +10274,8 @@
       <c r="L63" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T63" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U63" s="84" t="b">
-        <v>1</v>
+      <c r="S63" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -10519,26 +10323,23 @@
       <c r="L64" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N64" s="84" t="inlineStr">
+      <c r="M64" s="84" t="inlineStr">
         <is>
           <t>INFIS39031</t>
         </is>
       </c>
-      <c r="P64" s="84" t="inlineStr">
+      <c r="O64" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R64" s="84" t="inlineStr">
+      <c r="Q64" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22, DCN_TEC_09, DCN_TEC_14, DCN_TEC_13</t>
         </is>
       </c>
-      <c r="T64" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U64" s="84" t="b">
-        <v>0</v>
+      <c r="S64" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -10586,26 +10387,23 @@
       <c r="L65" s="84" t="b">
         <v>1</v>
       </c>
+      <c r="N65" s="84" t="inlineStr">
+        <is>
+          <t>INFIS39033</t>
+        </is>
+      </c>
       <c r="O65" s="84" t="inlineStr">
         <is>
-          <t>INFIS39033</t>
-        </is>
-      </c>
-      <c r="P65" s="84" t="inlineStr">
-        <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R65" s="84" t="inlineStr">
+      <c r="Q65" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22, DCN_TEC_09, DCN_TEC_14, DCN_TEC_13</t>
         </is>
       </c>
-      <c r="T65" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U65" s="84" t="b">
-        <v>0</v>
+      <c r="S65" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -10653,26 +10451,23 @@
       <c r="L66" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N66" s="84" t="inlineStr">
+      <c r="M66" s="84" t="inlineStr">
         <is>
           <t>FAMAT31011</t>
         </is>
       </c>
-      <c r="P66" s="84" t="inlineStr">
+      <c r="O66" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R66" s="84" t="inlineStr">
+      <c r="Q66" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22, DCN_TEC_14</t>
         </is>
       </c>
-      <c r="T66" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U66" s="84" t="b">
-        <v>0</v>
+      <c r="S66" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -10720,26 +10515,23 @@
       <c r="L67" s="84" t="b">
         <v>1</v>
       </c>
+      <c r="N67" s="84" t="inlineStr">
+        <is>
+          <t>INFIS39031</t>
+        </is>
+      </c>
       <c r="O67" s="84" t="inlineStr">
         <is>
-          <t>INFIS39031</t>
-        </is>
-      </c>
-      <c r="P67" s="84" t="inlineStr">
-        <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R67" s="84" t="inlineStr">
+      <c r="Q67" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22, DCN_TEC_14</t>
         </is>
       </c>
-      <c r="T67" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U67" s="84" t="b">
-        <v>0</v>
+      <c r="S67" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -10787,25 +10579,22 @@
       <c r="L68" s="84" t="b">
         <v>0</v>
       </c>
+      <c r="M68" s="84" t="inlineStr">
+        <is>
+          <t>INFIS39033</t>
+        </is>
+      </c>
       <c r="N68" s="84" t="inlineStr">
         <is>
-          <t>INFIS39033</t>
+          <t>INFIS39056</t>
         </is>
       </c>
       <c r="O68" s="84" t="inlineStr">
         <is>
-          <t>INFIS39056</t>
-        </is>
-      </c>
-      <c r="P68" s="84" t="inlineStr">
-        <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="T68" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U68" s="84" t="b">
+      <c r="S68" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10854,20 +10643,17 @@
       <c r="L69" s="84" t="b">
         <v>0</v>
       </c>
+      <c r="N69" s="84" t="inlineStr">
+        <is>
+          <t>INFIS31402</t>
+        </is>
+      </c>
       <c r="O69" s="84" t="inlineStr">
         <is>
-          <t>INFIS31402</t>
-        </is>
-      </c>
-      <c r="P69" s="84" t="inlineStr">
-        <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="T69" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U69" s="84" t="b">
+      <c r="S69" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10908,10 +10694,7 @@
       <c r="L70" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T70" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U70" s="84" t="b">
+      <c r="S70" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10960,25 +10743,22 @@
       <c r="L71" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N71" s="84" t="inlineStr">
+      <c r="M71" s="84" t="inlineStr">
         <is>
           <t>FAMAT31033</t>
         </is>
       </c>
-      <c r="P71" s="84" t="inlineStr">
+      <c r="O71" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R71" s="84" t="inlineStr">
+      <c r="Q71" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_06, DCN_BASE_28, DCN_BASE_33</t>
         </is>
       </c>
-      <c r="T71" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U71" s="84" t="b">
+      <c r="S71" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11027,21 +10807,18 @@
       <c r="L72" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P72" s="84" t="inlineStr">
+      <c r="O72" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R72" s="84" t="inlineStr">
+      <c r="Q72" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22</t>
         </is>
       </c>
-      <c r="T72" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U72" s="84" t="b">
-        <v>0</v>
+      <c r="S72" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -11081,10 +10858,7 @@
       <c r="L73" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T73" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U73" s="84" t="b">
+      <c r="S73" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11125,10 +10899,7 @@
       <c r="L74" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T74" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U74" s="84" t="b">
+      <c r="S74" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11177,25 +10948,22 @@
       <c r="L75" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N75" s="84" t="inlineStr">
+      <c r="M75" s="84" t="inlineStr">
         <is>
           <t>FEELT!SEG, FEELT!APMG</t>
         </is>
       </c>
-      <c r="P75" s="84" t="inlineStr">
+      <c r="O75" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R75" s="84" t="inlineStr">
+      <c r="Q75" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_06, DCN_BASE_11, DCN_BASE_04</t>
         </is>
       </c>
-      <c r="T75" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U75" s="84" t="b">
+      <c r="S75" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11236,10 +11004,7 @@
       <c r="L76" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T76" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U76" s="84" t="b">
+      <c r="S76" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11280,10 +11045,7 @@
       <c r="L77" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T77" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U77" s="84" t="b">
+      <c r="S77" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11324,10 +11086,7 @@
       <c r="L78" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T78" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U78" s="84" t="b">
+      <c r="S78" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11368,10 +11127,7 @@
       <c r="L79" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T79" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U79" s="84" t="b">
+      <c r="S79" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11412,10 +11168,7 @@
       <c r="L80" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T80" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U80" s="84" t="b">
+      <c r="S80" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11464,25 +11217,27 @@
       <c r="L81" s="84" t="b">
         <v>1</v>
       </c>
+      <c r="O81" s="84" t="inlineStr">
+        <is>
+          <t>CC2020_USUARIOS_ORGANIZACOES</t>
+        </is>
+      </c>
       <c r="P81" s="84" t="inlineStr">
         <is>
-          <t>CC2020_USUARIOS_ORGANIZACOES</t>
+          <t>RELACOES_ETNICO_RACIAIS, DIREITOS_HUMANOS, EDUCACAO_AMBIENTAL</t>
         </is>
       </c>
       <c r="Q81" s="84" t="inlineStr">
         <is>
-          <t>RELACOES_ETNICO_RACIAIS, DIREITOS_HUMANOS, EDUCACAO_AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="R81" s="84" t="inlineStr">
-        <is>
           <t>DCN_BASE_06, DCN_BASE_40, DCN_BASE_42, DCN_BASE_43, DCN_BASE_45</t>
         </is>
       </c>
-      <c r="T81" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U81" s="84" t="b">
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>ATUAR_ETICA_SUSTENTABILIDADE</t>
+        </is>
+      </c>
+      <c r="S81" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11523,10 +11278,7 @@
       <c r="L82" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T82" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U82" s="84" t="b">
+      <c r="S82" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11567,10 +11319,7 @@
       <c r="L83" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T83" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U83" s="84" t="b">
+      <c r="S83" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11619,26 +11368,23 @@
       <c r="L84" s="84" t="b">
         <v>1</v>
       </c>
+      <c r="O84" s="84" t="inlineStr">
+        <is>
+          <t>CC2020_USUARIOS_ORGANIZACOES</t>
+        </is>
+      </c>
       <c r="P84" s="84" t="inlineStr">
         <is>
-          <t>CC2020_USUARIOS_ORGANIZACOES</t>
+          <t>RELACOES_ETNICO_RACIAIS, DIREITOS_HUMANOS, EDUCACAO_AMBIENTAL, PREVENCAO_DESASTRES</t>
         </is>
       </c>
       <c r="Q84" s="84" t="inlineStr">
         <is>
-          <t>RELACOES_ETNICO_RACIAIS, DIREITOS_HUMANOS, EDUCACAO_AMBIENTAL, PREVENCAO_DESASTRES</t>
-        </is>
-      </c>
-      <c r="R84" s="84" t="inlineStr">
-        <is>
           <t>DCN_BASE_42, DCN_BASE_43, DCN_BASE_40, DCN_BASE_44, DCN_BASE_41, DCN_BASE_45</t>
         </is>
       </c>
-      <c r="T84" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U84" s="84" t="b">
-        <v>0</v>
+      <c r="S84" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -11686,20 +11432,22 @@
       <c r="L85" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P85" s="84" t="inlineStr">
+      <c r="O85" s="84" t="inlineStr">
         <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R85" s="84" t="inlineStr">
+      <c r="Q85" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_18, DCN_BASE_13, DCN_TEC_12, DCN_TEC_10, DCN_TEC_00, DCN_TEC_07</t>
         </is>
       </c>
-      <c r="T85" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U85" s="84" t="b">
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>DESENVOLVER_SISTEMAS_EMBARCADOS</t>
+        </is>
+      </c>
+      <c r="S85" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11740,15 +11488,12 @@
       <c r="L86" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="Q86" s="84" t="inlineStr">
+      <c r="P86" s="84" t="inlineStr">
         <is>
           <t>LIBRAS</t>
         </is>
       </c>
-      <c r="T86" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U86" s="84" t="b">
+      <c r="S86" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11789,15 +11534,12 @@
       <c r="L87" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="Q87" s="84" t="inlineStr">
+      <c r="P87" s="84" t="inlineStr">
         <is>
           <t>LIBRAS</t>
         </is>
       </c>
-      <c r="T87" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U87" s="84" t="b">
+      <c r="S87" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11838,10 +11580,7 @@
       <c r="L88" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T88" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U88" s="84" t="b">
+      <c r="S88" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11890,20 +11629,17 @@
       <c r="L89" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P89" s="84" t="inlineStr">
+      <c r="O89" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R89" s="84" t="inlineStr">
+      <c r="Q89" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_20, DCN_BASE_28, DCN_BASE_24, DCN_BASE_35</t>
         </is>
       </c>
-      <c r="T89" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U89" s="84" t="b">
+      <c r="S89" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11952,25 +11688,22 @@
       <c r="L90" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N90" s="84" t="inlineStr">
+      <c r="M90" s="84" t="inlineStr">
         <is>
           <t>ACE4</t>
         </is>
       </c>
-      <c r="P90" s="84" t="inlineStr">
+      <c r="O90" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_HUMANISTICA_GERAL</t>
         </is>
       </c>
-      <c r="R90" s="84" t="inlineStr">
+      <c r="Q90" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_44, DCN_BASE_42</t>
         </is>
       </c>
-      <c r="T90" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U90" s="84" t="b">
+      <c r="S90" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12019,26 +11752,23 @@
       <c r="L91" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N91" s="84" t="inlineStr">
+      <c r="M91" s="84" t="inlineStr">
         <is>
           <t>FAMAT31013</t>
         </is>
       </c>
-      <c r="P91" s="84" t="inlineStr">
+      <c r="O91" s="84" t="inlineStr">
         <is>
           <t>FORMACAO_BASICA_GERAL</t>
         </is>
       </c>
-      <c r="R91" s="84" t="inlineStr">
+      <c r="Q91" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22</t>
         </is>
       </c>
-      <c r="T91" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U91" s="84" t="b">
-        <v>0</v>
+      <c r="S91" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -12086,26 +11816,28 @@
       <c r="L92" s="84" t="b">
         <v>1</v>
       </c>
+      <c r="O92" s="84" t="inlineStr">
+        <is>
+          <t>CC2020_HARDWARE</t>
+        </is>
+      </c>
       <c r="P92" s="84" t="inlineStr">
         <is>
-          <t>CC2020_HARDWARE</t>
+          <t>EDUCACAO_AMBIENTAL, PREVENCAO_DESASTRES</t>
         </is>
       </c>
       <c r="Q92" s="84" t="inlineStr">
         <is>
-          <t>EDUCACAO_AMBIENTAL, PREVENCAO_DESASTRES</t>
-        </is>
-      </c>
-      <c r="R92" s="84" t="inlineStr">
-        <is>
           <t>DCN_BASE_18, DCN_BASE_45, DCN_BASE_22, DCN_TEC_07</t>
         </is>
       </c>
-      <c r="T92" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U92" s="84" t="b">
-        <v>0</v>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>ESPECIFICAR_INSTRUMENTACAO</t>
+        </is>
+      </c>
+      <c r="S92" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -12145,10 +11877,7 @@
       <c r="L93" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T93" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U93" s="84" t="b">
+      <c r="S93" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12189,10 +11918,7 @@
       <c r="L94" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T94" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U94" s="84" t="b">
+      <c r="S94" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12233,10 +11959,7 @@
       <c r="L95" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T95" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U95" s="84" t="b">
+      <c r="S95" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12277,10 +12000,7 @@
       <c r="L96" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T96" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U96" s="84" t="b">
+      <c r="S96" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12321,10 +12041,7 @@
       <c r="L97" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T97" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U97" s="84" t="b">
+      <c r="S97" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12365,11 +12082,8 @@
       <c r="L98" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T98" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U98" s="84" t="b">
-        <v>1</v>
+      <c r="S98" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -12409,15 +12123,12 @@
       <c r="L99" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="R99" s="84" t="inlineStr">
+      <c r="Q99" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_12</t>
         </is>
       </c>
-      <c r="T99" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U99" s="84" t="b">
+      <c r="S99" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12458,10 +12169,7 @@
       <c r="L100" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T100" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U100" s="84" t="b">
+      <c r="S100" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12502,10 +12210,7 @@
       <c r="L101" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T101" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U101" s="84" t="b">
+      <c r="S101" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12546,15 +12251,12 @@
       <c r="L102" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="R102" s="84" t="inlineStr">
+      <c r="Q102" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_26</t>
         </is>
       </c>
-      <c r="T102" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U102" s="84" t="b">
+      <c r="S102" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12595,10 +12297,7 @@
       <c r="L103" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T103" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U103" s="84" t="b">
+      <c r="S103" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12627,11 +12326,8 @@
       <c r="L104" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T104" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U104" s="84" t="b">
-        <v>1</v>
+      <c r="S104" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -12659,11 +12355,8 @@
       <c r="L105" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T105" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U105" s="84" t="b">
-        <v>1</v>
+      <c r="S105" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -12691,11 +12384,8 @@
       <c r="L106" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T106" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U106" s="84" t="b">
-        <v>1</v>
+      <c r="S106" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -12723,11 +12413,8 @@
       <c r="L107" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T107" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U107" s="84" t="b">
-        <v>1</v>
+      <c r="S107" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -12767,15 +12454,12 @@
       <c r="L108" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="R108" s="84" t="inlineStr">
+      <c r="Q108" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_26</t>
         </is>
       </c>
-      <c r="T108" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U108" s="84" t="b">
+      <c r="S108" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12816,10 +12500,7 @@
       <c r="L109" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T109" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U109" s="84" t="b">
+      <c r="S109" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12860,10 +12541,7 @@
       <c r="L110" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T110" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U110" s="84" t="b">
+      <c r="S110" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12904,10 +12582,7 @@
       <c r="L111" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T111" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U111" s="84" t="b">
+      <c r="S111" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12956,26 +12631,23 @@
       <c r="L112" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N112" s="84" t="inlineStr">
+      <c r="M112" s="84" t="inlineStr">
         <is>
           <t>FAMAT31031</t>
         </is>
       </c>
-      <c r="P112" s="84" t="inlineStr">
+      <c r="O112" s="84" t="inlineStr">
         <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R112" s="84" t="inlineStr">
+      <c r="Q112" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_22, DCN_BASE_34, DCN_TEC_03</t>
         </is>
       </c>
-      <c r="T112" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U112" s="84" t="b">
-        <v>0</v>
+      <c r="S112" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -13023,20 +12695,17 @@
       <c r="L113" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P113" s="84" t="inlineStr">
+      <c r="O113" s="84" t="inlineStr">
         <is>
           <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
       </c>
-      <c r="R113" s="84" t="inlineStr">
+      <c r="Q113" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_21, DCN_BASE_33, DCN_BASE_32, DCN_BASE_19</t>
         </is>
       </c>
-      <c r="T113" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U113" s="84" t="b">
+      <c r="S113" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -13077,10 +12746,7 @@
       <c r="L114" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T114" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U114" s="84" t="b">
+      <c r="S114" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13121,10 +12787,7 @@
       <c r="L115" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T115" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U115" s="84" t="b">
+      <c r="S115" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13165,10 +12828,7 @@
       <c r="L116" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T116" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U116" s="84" t="b">
+      <c r="S116" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13217,25 +12877,22 @@
       <c r="L117" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N117" s="84" t="inlineStr">
+      <c r="M117" s="84" t="inlineStr">
         <is>
           <t>FEELT!PP</t>
         </is>
       </c>
-      <c r="P117" s="84" t="inlineStr">
+      <c r="O117" s="84" t="inlineStr">
         <is>
           <t>CC2020_MODELAGEM_SISTEMAS</t>
         </is>
       </c>
-      <c r="R117" s="84" t="inlineStr">
+      <c r="Q117" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_33, DCN_BASE_02</t>
         </is>
       </c>
-      <c r="T117" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U117" s="84" t="b">
+      <c r="S117" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -13276,10 +12933,7 @@
       <c r="L118" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T118" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U118" s="84" t="b">
+      <c r="S118" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13320,10 +12974,7 @@
       <c r="L119" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T119" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U119" s="84" t="b">
+      <c r="S119" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13364,10 +13015,7 @@
       <c r="L120" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T120" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U120" s="84" t="b">
+      <c r="S120" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13416,25 +13064,22 @@
       <c r="L121" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N121" s="84" t="inlineStr">
+      <c r="M121" s="84" t="inlineStr">
         <is>
           <t>FEELT!PS</t>
         </is>
       </c>
-      <c r="P121" s="84" t="inlineStr">
+      <c r="O121" s="84" t="inlineStr">
         <is>
           <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
       </c>
-      <c r="R121" s="84" t="inlineStr">
+      <c r="Q121" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_33</t>
         </is>
       </c>
-      <c r="T121" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U121" s="84" t="b">
+      <c r="S121" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -13483,20 +13128,17 @@
       <c r="L122" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="P122" s="84" t="inlineStr">
+      <c r="O122" s="84" t="inlineStr">
         <is>
           <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
       </c>
-      <c r="R122" s="84" t="inlineStr">
+      <c r="Q122" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_33</t>
         </is>
       </c>
-      <c r="T122" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U122" s="84" t="b">
+      <c r="S122" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -13545,21 +13187,18 @@
       <c r="L123" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N123" s="84" t="inlineStr">
+      <c r="M123" s="84" t="inlineStr">
         <is>
           <t>FEELT!BD</t>
         </is>
       </c>
-      <c r="P123" s="84" t="inlineStr">
+      <c r="O123" s="84" t="inlineStr">
         <is>
           <t>CC2020_MODELAGEM_SISTEMAS</t>
         </is>
       </c>
-      <c r="T123" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U123" s="84" t="b">
-        <v>1</v>
+      <c r="S123" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -13599,10 +13238,7 @@
       <c r="L124" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T124" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U124" s="84" t="b">
+      <c r="S124" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13651,21 +13287,18 @@
       <c r="L125" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N125" s="84" t="inlineStr">
+      <c r="M125" s="84" t="inlineStr">
         <is>
           <t>FEELT31523</t>
         </is>
       </c>
-      <c r="P125" s="84" t="inlineStr">
+      <c r="O125" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="T125" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U125" s="84" t="b">
-        <v>1</v>
+      <c r="S125" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -13705,16 +13338,13 @@
       <c r="L126" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="R126" s="84" t="inlineStr">
+      <c r="Q126" s="84" t="inlineStr">
         <is>
           <t>DCN_TEC_01</t>
         </is>
       </c>
-      <c r="T126" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U126" s="84" t="b">
-        <v>1</v>
+      <c r="S126" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -13762,26 +13392,23 @@
       <c r="L127" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N127" s="84" t="inlineStr">
+      <c r="M127" s="84" t="inlineStr">
         <is>
           <t>FEELT!SO</t>
         </is>
       </c>
-      <c r="P127" s="84" t="inlineStr">
+      <c r="O127" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R127" s="84" t="inlineStr">
+      <c r="Q127" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_04, DCN_BASE_39, DCN_TEC_04</t>
         </is>
       </c>
-      <c r="T127" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U127" s="84" t="b">
-        <v>0</v>
+      <c r="S127" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -13829,26 +13456,23 @@
       <c r="L128" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N128" s="84" t="inlineStr">
+      <c r="M128" s="84" t="inlineStr">
         <is>
           <t>FEELT31724</t>
         </is>
       </c>
-      <c r="P128" s="84" t="inlineStr">
+      <c r="O128" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R128" s="84" t="inlineStr">
+      <c r="Q128" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_04, DCN_BASE_39, DCN_TEC_04</t>
         </is>
       </c>
-      <c r="T128" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U128" s="84" t="b">
-        <v>0</v>
+      <c r="S128" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -13888,10 +13512,7 @@
       <c r="L129" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T129" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U129" s="84" t="b">
+      <c r="S129" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13932,10 +13553,7 @@
       <c r="L130" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T130" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U130" s="84" t="b">
+      <c r="S130" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13976,10 +13594,7 @@
       <c r="L131" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T131" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U131" s="84" t="b">
+      <c r="S131" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14020,10 +13635,7 @@
       <c r="L132" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T132" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U132" s="84" t="b">
+      <c r="S132" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14064,11 +13676,8 @@
       <c r="L133" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T133" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U133" s="84" t="b">
-        <v>1</v>
+      <c r="S133" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -14108,11 +13717,8 @@
       <c r="L134" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T134" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U134" s="84" t="b">
-        <v>1</v>
+      <c r="S134" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -14152,20 +13758,17 @@
       <c r="L135" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N135" s="84" t="inlineStr">
+      <c r="M135" s="84" t="inlineStr">
         <is>
           <t>FEELT!SCON</t>
         </is>
       </c>
-      <c r="R135" s="84" t="inlineStr">
+      <c r="Q135" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_16</t>
         </is>
       </c>
-      <c r="T135" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U135" s="84" t="b">
+      <c r="S135" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14214,25 +13817,22 @@
       <c r="L136" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N136" s="84" t="inlineStr">
+      <c r="M136" s="84" t="inlineStr">
         <is>
           <t>FEELT31724</t>
         </is>
       </c>
-      <c r="P136" s="84" t="inlineStr">
+      <c r="O136" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R136" s="84" t="inlineStr">
+      <c r="Q136" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_11, DCN_BASE_00, DCN_BASE_04</t>
         </is>
       </c>
-      <c r="T136" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U136" s="84" t="b">
+      <c r="S136" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14273,10 +13873,7 @@
       <c r="L137" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T137" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U137" s="84" t="b">
+      <c r="S137" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14325,25 +13922,22 @@
       <c r="L138" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N138" s="84" t="inlineStr">
+      <c r="M138" s="84" t="inlineStr">
         <is>
           <t>FEELT31523</t>
         </is>
       </c>
-      <c r="P138" s="84" t="inlineStr">
+      <c r="O138" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R138" s="84" t="inlineStr">
+      <c r="Q138" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_39, DCN_BASE_10, DCN_BASE_00, DCN_BASE_05, DCN_TEC_05, DCN_TEC_00, DCN_TEC_06</t>
         </is>
       </c>
-      <c r="T138" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U138" s="84" t="b">
+      <c r="S138" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14384,10 +13978,7 @@
       <c r="L139" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T139" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U139" s="84" t="b">
+      <c r="S139" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14436,26 +14027,23 @@
       <c r="L140" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N140" s="84" t="inlineStr">
+      <c r="M140" s="84" t="inlineStr">
         <is>
           <t>FEELT!LMD</t>
         </is>
       </c>
-      <c r="P140" s="84" t="inlineStr">
+      <c r="O140" s="84" t="inlineStr">
         <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R140" s="84" t="inlineStr">
+      <c r="Q140" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_37, DCN_TEC_10, DCN_TEC_00</t>
         </is>
       </c>
-      <c r="T140" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U140" s="84" t="b">
-        <v>0</v>
+      <c r="S140" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -14503,26 +14091,23 @@
       <c r="L141" s="84" t="b">
         <v>1</v>
       </c>
+      <c r="N141" s="84" t="inlineStr">
+        <is>
+          <t>FEELT31409</t>
+        </is>
+      </c>
       <c r="O141" s="84" t="inlineStr">
         <is>
-          <t>FEELT31409</t>
-        </is>
-      </c>
-      <c r="P141" s="84" t="inlineStr">
-        <is>
           <t>CC2020_HARDWARE</t>
         </is>
       </c>
-      <c r="R141" s="84" t="inlineStr">
+      <c r="Q141" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_37, DCN_TEC_10, DCN_TEC_00</t>
         </is>
       </c>
-      <c r="T141" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U141" s="84" t="b">
-        <v>0</v>
+      <c r="S141" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -14570,25 +14155,22 @@
       <c r="L142" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N142" s="84" t="inlineStr">
+      <c r="M142" s="84" t="inlineStr">
         <is>
           <t>FEELT31724</t>
         </is>
       </c>
-      <c r="P142" s="84" t="inlineStr">
+      <c r="O142" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R142" s="84" t="inlineStr">
+      <c r="Q142" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_39, DCN_BASE_09, DCN_BASE_10, DCN_BASE_15, DCN_TEC_04</t>
         </is>
       </c>
-      <c r="T142" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U142" s="84" t="b">
+      <c r="S142" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14629,10 +14211,7 @@
       <c r="L143" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T143" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U143" s="84" t="b">
+      <c r="S143" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14673,10 +14252,7 @@
       <c r="L144" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T144" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U144" s="84" t="b">
+      <c r="S144" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14725,25 +14301,27 @@
       <c r="L145" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N145" s="84" t="inlineStr">
+      <c r="M145" s="84" t="inlineStr">
         <is>
           <t>FEELT31628</t>
         </is>
       </c>
-      <c r="P145" s="84" t="inlineStr">
+      <c r="O145" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R145" s="84" t="inlineStr">
+      <c r="Q145" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_18, DCN_BASE_34, DCN_TEC_05, DCN_TEC_06</t>
         </is>
       </c>
-      <c r="T145" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U145" s="84" t="b">
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>PROJETAR_SISTEMAS_CONTROLE</t>
+        </is>
+      </c>
+      <c r="S145" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14792,26 +14370,28 @@
       <c r="L146" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N146" s="84" t="inlineStr">
+      <c r="M146" s="84" t="inlineStr">
         <is>
           <t>FEELT31401, FEELT!SO</t>
         </is>
       </c>
-      <c r="P146" s="84" t="inlineStr">
+      <c r="O146" s="84" t="inlineStr">
         <is>
           <t>CC2020_ARQUITETURA_INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="R146" s="84" t="inlineStr">
+      <c r="Q146" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_18, DCN_BASE_00, DCN_BASE_05, DCN_BASE_13, DCN_TEC_00, DCN_TEC_10, DCN_TEC_02, DCN_TEC_07, DCN_TEC_05, DCN_TEC_06</t>
         </is>
       </c>
-      <c r="T146" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U146" s="84" t="b">
-        <v>0</v>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>DESENVOLVER_SISTEMAS_EMBARCADOS</t>
+        </is>
+      </c>
+      <c r="S146" s="84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -14851,15 +14431,12 @@
       <c r="L147" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="N147" s="84" t="inlineStr">
+      <c r="M147" s="84" t="inlineStr">
         <is>
           <t>FEELT31523</t>
         </is>
       </c>
-      <c r="T147" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U147" s="84" t="b">
+      <c r="S147" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14908,25 +14485,22 @@
       <c r="L148" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N148" s="84" t="inlineStr">
+      <c r="M148" s="84" t="inlineStr">
         <is>
           <t>FEELT!PP, FEELT!AOC</t>
         </is>
       </c>
-      <c r="P148" s="84" t="inlineStr">
+      <c r="O148" s="84" t="inlineStr">
         <is>
           <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
       </c>
-      <c r="R148" s="84" t="inlineStr">
+      <c r="Q148" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_00</t>
         </is>
       </c>
-      <c r="T148" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U148" s="84" t="b">
+      <c r="S148" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14967,10 +14541,7 @@
       <c r="L149" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="T149" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U149" s="84" t="b">
+      <c r="S149" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15011,10 +14582,7 @@
       <c r="L150" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T150" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U150" s="84" t="b">
+      <c r="S150" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15063,25 +14631,22 @@
       <c r="L151" s="84" t="b">
         <v>1</v>
       </c>
-      <c r="N151" s="84" t="inlineStr">
+      <c r="M151" s="84" t="inlineStr">
         <is>
           <t>FEELT!AA</t>
         </is>
       </c>
-      <c r="P151" s="84" t="inlineStr">
+      <c r="O151" s="84" t="inlineStr">
         <is>
           <t>CC2020_FUNDAMENTOS_SOFTWARE</t>
         </is>
       </c>
-      <c r="R151" s="84" t="inlineStr">
+      <c r="Q151" s="84" t="inlineStr">
         <is>
           <t>DCN_BASE_27, DCN_BASE_30, DCN_BASE_29, DCN_BASE_35</t>
         </is>
       </c>
-      <c r="T151" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U151" s="84" t="b">
+      <c r="S151" s="84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -15110,11 +14675,8 @@
       <c r="L152" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T152" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U152" s="84" t="b">
-        <v>1</v>
+      <c r="S152" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -15142,11 +14704,8 @@
       <c r="L153" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T153" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U153" s="84" t="b">
-        <v>1</v>
+      <c r="S153" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -15174,11 +14733,8 @@
       <c r="L154" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T154" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U154" s="84" t="b">
-        <v>1</v>
+      <c r="S154" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -15206,11 +14762,8 @@
       <c r="L155" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T155" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U155" s="84" t="b">
-        <v>1</v>
+      <c r="S155" s="84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -15250,10 +14803,7 @@
       <c r="L156" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T156" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U156" s="84" t="b">
+      <c r="S156" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15294,10 +14844,7 @@
       <c r="L157" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T157" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U157" s="84" t="b">
+      <c r="S157" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15338,10 +14885,7 @@
       <c r="L158" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T158" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U158" s="84" t="b">
+      <c r="S158" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15382,10 +14926,7 @@
       <c r="L159" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T159" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U159" s="84" t="b">
+      <c r="S159" s="84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15426,10 +14967,7 @@
       <c r="L160" s="84" t="b">
         <v>0</v>
       </c>
-      <c r="T160" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="U160" s="84" t="b">
+      <c r="S160" s="84" t="b">
         <v>0</v>
       </c>
     </row>
